--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_8/262FL_10A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_8/262FL_10A.xlsx
@@ -8620,7 +8620,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
